--- a/branches/chore/snomed-2026-07-01/StructureDefinition-mii-pr-molgen-mikrosatelliteninstabilitaet.xlsx
+++ b/branches/chore/snomed-2026-07-01/StructureDefinition-mii-pr-molgen-mikrosatelliteninstabilitaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:35:16+00:00</t>
+    <t>2026-09-04T10:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
